--- a/artfynd/A 23548-2026 artfynd.xlsx
+++ b/artfynd/A 23548-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6006313</v>
+        <v>119137192</v>
       </c>
       <c r="B2" t="n">
-        <v>96375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223620</v>
+        <v>221333</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsnattviol × grönvit nattviol</t>
+          <t>Backklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia × chlorantha</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Trifolium montanum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>mellan Grop och Ladusveden, Upl</t>
+          <t>Sandbacken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>715902.8731887767</v>
+        <v>715925</v>
       </c>
       <c r="R2" t="n">
-        <v>6647882.452676741</v>
+        <v>6647694</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-06-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-06-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Höjd 50 cm, ax 12 cm, 19 glest sittande blommor. Blomma: läpp 13 mm, grön yttre del, gulgrön inre. Kalkblad annars gräddvita. Sporre 35 mm, grön, tunn. Pollinier mkt grova, parallella.</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,30 +761,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Blandskog, glänta, frisk mark</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Karin Agstam-Norlin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Karin Agstam-Norlin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69685323</v>
+        <v>6006313</v>
       </c>
       <c r="B3" t="n">
-        <v>99097</v>
+        <v>99162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,30 +791,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6010645</v>
+        <v>223620</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol × grönvit nattviol</t>
+          <t>Ängsnattviol × grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia × chlorantha</t>
+          <t>Platanthera bifolia subsp. bifolia × chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mellan Grop och Ladusveden, Upl</t>
+          <t>mellan Grop och Ladusveden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>715899</v>
+        <v>715903</v>
       </c>
       <c r="R3" t="n">
-        <v>6647857</v>
+        <v>6647882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1995-01-01</t>
+          <t>1995-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1995-12-31</t>
+          <t>1995-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter. 1 ex, Fotobelägg</t>
+          <t>Höjd 50 cm, ax 12 cm, 19 glest sittande blommor. Blomma: läpp 13 mm, grön yttre del, gulgrön inre. Kalkblad annars gräddvita. Sporre 35 mm, grön, tunn. Pollinier mkt grova, parallella.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,21 +879,124 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>glänta i blandskog, på frisk mark</t>
+          <t>Blandskog, glänta, frisk mark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69685323</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99238</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6010645</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattviol × grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia × chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellan Grop och Ladusveden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>715899</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6647857</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Söderby-Karl</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1995-01-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1995-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. 1 ex, Fotobelägg</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>glänta i blandskog, på frisk mark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Joakim Ekman</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>

--- a/artfynd/A 23548-2026 artfynd.xlsx
+++ b/artfynd/A 23548-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119137192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6006313</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,8 +1016,18 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69685323</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>